--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487702_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487702_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9797</v>
+        <v>6.67</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7354</v>
+        <v>4.2349</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2443</v>
+        <v>2.4351</v>
       </c>
       <c r="G2" t="n">
         <v>2.1673</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4125</v>
+        <v>1.1028</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9724</v>
+        <v>0.4719</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4401</v>
+        <v>0.6309</v>
       </c>
       <c r="V2" t="n">
         <v>3.0119</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6198</v>
+        <v>6.0276</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0086</v>
+        <v>5.0076</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6112</v>
+        <v>1.0201</v>
       </c>
       <c r="G3" t="n">
         <v>4.3637</v>
@@ -688,13 +688,13 @@
         <v>0.194</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4502</v>
+        <v>0.858</v>
       </c>
       <c r="T3" t="n">
-        <v>1.578</v>
+        <v>0.577</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1278</v>
+        <v>0.281</v>
       </c>
       <c r="V3" t="n">
         <v>0.6119</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7237</v>
+        <v>4.2965</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1708</v>
+        <v>1.4711</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5529</v>
+        <v>2.8254</v>
       </c>
       <c r="G4" t="n">
         <v>2.0039</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5451</v>
+        <v>1.1179</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1222</v>
+        <v>0.4225</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4229</v>
+        <v>0.6954</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3776</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3699</v>
+        <v>2.8248</v>
       </c>
       <c r="E5" t="n">
         <v>1.098</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2719</v>
+        <v>1.7268</v>
       </c>
       <c r="G5" t="n">
         <v>1.2296</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1568</v>
+        <v>1.6117</v>
       </c>
       <c r="T5" t="n">
         <v>0.4262</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7306</v>
+        <v>1.1856</v>
       </c>
       <c r="V5" t="n">
         <v>2.1179</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4877</v>
+        <v>0.3014</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3646</v>
+        <v>0.5419</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8523</v>
+        <v>-0.2405</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1826</v>
+        <v>1.1495</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1648</v>
+        <v>0.1747</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0178</v>
+        <v>0.9749</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1259</v>
+        <v>0.4443</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0463</v>
+        <v>0.4037</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1723</v>
+        <v>0.0406</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3085</v>
+        <v>0.7052</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.229</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1901</v>
+        <v>0.9343</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.6866</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8508</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.544</v>
+        <v>0.3757</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0595</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6035</v>
+        <v>0.2782</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4477</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>3.6716</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-1.2239</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4261</v>
+        <v>0.0708</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1415</v>
+        <v>-1.4486</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5675</v>
+        <v>1.5195</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1495</v>
+        <v>0.9795</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1747</v>
+        <v>-0.4424</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9749</v>
+        <v>1.422</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4443</v>
+        <v>1.138</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4037</v>
+        <v>0.3666</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0406</v>
+        <v>0.7713</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7052</v>
+        <v>-0.1584</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.229</v>
+        <v>-0.8091</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9343</v>
+        <v>0.6506</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3517</v>
+        <v>0.1391</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>0.0134</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0489</v>
+        <v>0.1256</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MENDOZA ALVAREZ</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.457</v>
+        <v>0.0521</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4016</v>
+        <v>-1.0643</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0554</v>
+        <v>1.1164</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1256</v>
+        <v>0.1826</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3487</v>
+        <v>0.1648</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7769</v>
+        <v>0.0178</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2931</v>
+        <v>-0.1259</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3337</v>
+        <v>1.0463</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6267</v>
+        <v>-1.1723</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8325</v>
+        <v>0.3085</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6824</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1502</v>
+        <v>1.1901</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9702</v>
+        <v>-3.6866</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-4.8508</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>1.085</v>
+        <v>1.1084</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6079</v>
+        <v>0.2408</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4772</v>
+        <v>0.8676</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5537</v>
+        <v>2.4477</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2239</v>
+        <v>3.6716</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>J. MENDOZA ALVAREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0025</v>
+        <v>-1.3118</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2494</v>
+        <v>-0.9021</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2469</v>
+        <v>-0.4097</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9795</v>
+        <v>-2.1256</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4424</v>
+        <v>-1.3487</v>
       </c>
       <c r="I9" t="n">
-        <v>1.422</v>
+        <v>-0.7769</v>
       </c>
       <c r="J9" t="n">
-        <v>1.138</v>
+        <v>-0.2931</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3666</v>
+        <v>0.3337</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7713</v>
+        <v>-0.6267</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1584</v>
+        <v>-1.8325</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8091</v>
+        <v>-1.6824</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6506</v>
+        <v>-0.1502</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3881</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9343</v>
+        <v>0.2302</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7874</v>
+        <v>0.1074</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1469</v>
+        <v>0.1228</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6597</v>
+        <v>1.5537</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6597</v>
+        <v>1.2239</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>G. MORENO ABAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8752</v>
+        <v>-1.8461</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.909</v>
+        <v>-0.7222</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9663</v>
+        <v>-1.1239</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4173</v>
+        <v>-0.7668</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1854</v>
+        <v>-0.3609</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2319</v>
+        <v>-0.406</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0612</v>
+        <v>0.3295</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0206</v>
+        <v>0.3295</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4785</v>
+        <v>-1.0964</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.206</v>
+        <v>-0.6904</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2725</v>
+        <v>-0.406</v>
       </c>
       <c r="P10" t="n">
         <v>-0.5821</v>
@@ -1234,28 +1234,28 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0182</v>
+        <v>-0.2151</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0182</v>
+        <v>-0.1335</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. MORENO ABAD</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9462</v>
+        <v>-1.848</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8223</v>
+        <v>-0.909</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1239</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7668</v>
+        <v>-0.4173</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3609</v>
+        <v>-0.1854</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.406</v>
+        <v>-0.2319</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3295</v>
+        <v>0.0612</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3295</v>
+        <v>0.0206</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.0406</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0964</v>
+        <v>-0.4785</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6904</v>
+        <v>-0.206</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.406</v>
+        <v>-0.2725</v>
       </c>
       <c r="P11" t="n">
         <v>-0.5821</v>
@@ -1312,22 +1312,22 @@
         <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3152</v>
+        <v>0.0454</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1817</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1335</v>
+        <v>0.0454</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0816</v>
+        <v>-2.8453</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6577</v>
+        <v>-3.5576</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.7124</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7882</v>
@@ -1390,13 +1390,13 @@
         <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4307</v>
+        <v>-0.1943</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3095</v>
+        <v>-0.1733</v>
       </c>
       <c r="V12" t="n">
         <v>0.6597</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.3922</v>
+        <v>12.392</v>
       </c>
       <c r="E13" t="n">
-        <v>3.749699999999999</v>
+        <v>3.749700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>8.642500000000002</v>
+        <v>8.6426</v>
       </c>
       <c r="G13" t="n">
         <v>7.978200000000001</v>
@@ -1456,10 +1456,10 @@
         <v>-7.612800000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>7.8966</v>
+        <v>7.896599999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-8.7315</v>
+        <v>-8.731499999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.4331</v>
@@ -1468,13 +1468,13 @@
         <v>9.701799999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>6.179900000000001</v>
+        <v>6.179799999999999</v>
       </c>
       <c r="T13" t="n">
         <v>2.2542</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9259</v>
+        <v>3.9257</v>
       </c>
       <c r="V13" t="n">
         <v>6.9655</v>
@@ -1483,7 +1483,7 @@
         <v>12.2343</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.2686</v>
+        <v>-5.268599999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4158</v>
+        <v>3.8618</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7867</v>
+        <v>2.2872</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6291</v>
+        <v>1.5746</v>
       </c>
       <c r="G14" t="n">
         <v>1.2797</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1523</v>
+        <v>-0.7063</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7874</v>
+        <v>-0.2869</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3649</v>
+        <v>-0.4194</v>
       </c>
       <c r="V14" t="n">
         <v>0.96</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0133</v>
+        <v>1.7953</v>
       </c>
       <c r="E15" t="n">
         <v>1.4949</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5184</v>
+        <v>0.3003</v>
       </c>
       <c r="G15" t="n">
         <v>0.9330000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>2.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6063</v>
+        <v>-0.8244</v>
       </c>
       <c r="T15" t="n">
         <v>-0.6046</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0018</v>
+        <v>-0.2198</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2239</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>A. OLMEDO VELASCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6669</v>
+        <v>0.6994</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4754</v>
+        <v>1.2664</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1916</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9074</v>
+        <v>0.2225</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8496</v>
+        <v>1.7145</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0578</v>
+        <v>-1.492</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5422</v>
+        <v>1.7613</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.174</v>
+        <v>2.5582</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6318</v>
+        <v>-0.7968</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3652</v>
+        <v>-1.5389</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6756</v>
+        <v>-0.8437</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6896</v>
+        <v>-0.6952</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9702</v>
+        <v>2.5224</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1045</v>
+        <v>3.6866</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0504</v>
+        <v>-1.7816</v>
       </c>
       <c r="T16" t="n">
-        <v>1.034</v>
+        <v>-1.1188</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0164</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5537</v>
+        <v>-0.2639</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1179</v>
+        <v>1.788</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5642</v>
+        <v>-2.0519</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VILASANCHEZ FREIJOMIL</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2486</v>
+        <v>-0.0254</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1019</v>
+        <v>-1.0261</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1467</v>
+        <v>1.0008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4216</v>
+        <v>-1.9074</v>
       </c>
       <c r="H18" t="n">
-        <v>0.346</v>
+        <v>-1.8496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0756</v>
+        <v>-0.0578</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1522</v>
+        <v>-0.5422</v>
       </c>
       <c r="K18" t="n">
-        <v>1.071</v>
+        <v>-1.174</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.6318</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7306</v>
+        <v>-1.3652</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.725</v>
+        <v>-0.6756</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0056</v>
+        <v>-0.6896</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5821</v>
+        <v>3.1045</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8371</v>
+        <v>-0.6418</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6079</v>
+        <v>-0.4675</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2293</v>
+        <v>-0.1744</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3481</v>
+        <v>1.5537</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>2.1179</v>
       </c>
       <c r="X18" t="n">
-        <v>0.066</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. OLMEDO VELASCO</t>
+          <t>J. VILASANCHEZ FREIJOMIL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6832</v>
+        <v>-0.4699</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2654</v>
+        <v>-0.3986</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9485</v>
+        <v>-0.0713</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2225</v>
+        <v>0.4216</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7145</v>
+        <v>0.346</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.492</v>
+        <v>0.0756</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7613</v>
+        <v>1.1522</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5582</v>
+        <v>1.071</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7968</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5389</v>
+        <v>-0.7306</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8437</v>
+        <v>-0.725</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6952</v>
+        <v>-0.0056</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5224</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>3.6866</v>
+        <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.1642</v>
+        <v>0.1186</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.1198</v>
+        <v>0.1074</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0444</v>
+        <v>0.0112</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2639</v>
+        <v>0.3481</v>
       </c>
       <c r="W19" t="n">
-        <v>1.788</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.0519</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>P. DOMINGUEZ LORENZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9762</v>
+        <v>-1.6262</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3379</v>
+        <v>-2.465</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6383</v>
+        <v>0.8388</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5621</v>
+        <v>-1.002</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0297</v>
+        <v>0.6574</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5917</v>
+        <v>-1.6594</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1824</v>
+        <v>-0.8841</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4037</v>
+        <v>-0.1812</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5861</v>
+        <v>-0.7029</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3796</v>
+        <v>-0.1179</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.374</v>
+        <v>0.8387</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0056</v>
+        <v>-0.9565</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9702</v>
+        <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8794999999999999</v>
+        <v>-1.2242</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6684</v>
+        <v>-0.6107</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2111</v>
+        <v>-0.6135</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0997</v>
+        <v>-0.5642</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.44</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1669</v>
+        <v>-2.0217</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0416</v>
+        <v>-2.1417</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1253</v>
+        <v>0.12</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0572</v>
@@ -2092,13 +2092,13 @@
         <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6115</v>
+        <v>-0.4663</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2412</v>
+        <v>-0.3413</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3703</v>
+        <v>-0.125</v>
       </c>
       <c r="V21" t="n">
         <v>0.1137</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. DOMINGUEZ LORENZO</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4993</v>
+        <v>-2.722</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0656</v>
+        <v>-1.8384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5663</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.002</v>
+        <v>-0.5621</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6574</v>
+        <v>0.0297</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6594</v>
+        <v>-0.5917</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8841</v>
+        <v>-0.1824</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1812</v>
+        <v>0.4037</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7029</v>
+        <v>-0.5861</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1179</v>
+        <v>-0.3796</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8387</v>
+        <v>-0.374</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9565</v>
+        <v>-0.0056</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1344</v>
+        <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0974</v>
+        <v>0.1337</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2113</v>
+        <v>0.1679</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.886</v>
+        <v>-0.0342</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5642</v>
+        <v>-2.0997</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5642</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6134</v>
+        <v>-5.4315</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3848</v>
+        <v>-2.2847</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2286</v>
+        <v>-3.1469</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5293</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6364</v>
+        <v>-0.4545</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.424</v>
+        <v>-0.3239</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4477</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4097</v>
+        <v>-7.0638</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.937</v>
+        <v>-3.5366</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4727</v>
+        <v>-3.5272</v>
       </c>
       <c r="G24" t="n">
         <v>-2.777</v>
@@ -2326,13 +2326,13 @@
         <v>1.1642</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.679</v>
+        <v>-0.3331</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8479</v>
+        <v>-0.4475</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1689</v>
+        <v>0.1144</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9537</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.3922</v>
+        <v>-12.3921</v>
       </c>
       <c r="E25" t="n">
         <v>-8.0307</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.3613</v>
+        <v>-4.361499999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-7.9782</v>
       </c>
       <c r="H25" t="n">
-        <v>3.394299999999999</v>
+        <v>3.3943</v>
       </c>
       <c r="I25" t="n">
         <v>-11.3724</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2838000000000005</v>
+        <v>-0.2838000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>7.6128</v>
+        <v>7.612799999999999</v>
       </c>
       <c r="L25" t="n">
         <v>-7.8964</v>
@@ -2389,7 +2389,7 @@
         <v>-7.6944</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.218399999999999</v>
+        <v>-4.2184</v>
       </c>
       <c r="O25" t="n">
         <v>-3.4759</v>
@@ -2404,13 +2404,13 @@
         <v>18.4332</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.180100000000001</v>
+        <v>-6.1799</v>
       </c>
       <c r="T25" t="n">
         <v>-3.9259</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.2541</v>
+        <v>-2.2542</v>
       </c>
       <c r="V25" t="n">
         <v>-6.9657</v>
